--- a/04_DESIGN_TABLES/DesignTable_6807_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6807_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS2"/>
+  <dimension ref="A1:BS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1000,6 +1000,476 @@
       <c r="BS2" t="inlineStr">
         <is>
           <t>6807-06-06-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>6807-16-16-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="H3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.87603</v>
+      </c>
+      <c r="J3" t="n">
+        <v>75</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.5975</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.87603</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.5975</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.75698</v>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>6807-16-16-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>90 deg Adjustable Male ORB x Adjustable Male ORB Elbow, 1 5/16-12 (adjustable male ORB) x 1 5/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>6807</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): legs / locknut hexes / flats / bores from the Brennan TFA catalog p.44; ORB majors from the end library | 2026-10-20 (batch 19 D_geom): DataStatus MISSING -&gt; ASSUMED - one source (Brennan TFA catalog p.44 TFA-p044-t01); generated with the batch-17 6807 SPEC | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = the row body hex Y (no male JIC leg, so no 2603HX raise), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing; end-library values (Q-TRANSFER-ENDLIB, user 2026-10-08 'reuse end details - yes'): adjustable ORB tip-to-body-face = Air-Way 6801 ORB_I3 of the same ORB size (= the Brennan 6801 STEPs); adjustable ORB thread length = the ORB end library (6401 / 6405 / 6410 tables, = Air-Way 6801 at every dash); adjustable ORB O-ring undercut dia = the ORB end library (6401 / 6405 / 6410 tables, = Air-Way 6801 at every dash); two adjustable ORB legs on one 90 deg elbow forging (OMi "MAORB - MAORB 90 deg Elbow Forged"; no Brennan 6807 STEP seen: the body form - 2500HX hex arms + 30deg corner puck, each ORB leg = the ORB leg of the accepted 6801 forging - is ASSUMED from the Brennan 6801-XX-XX-NWO-FG STEPs, shape only)</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.44 alone; marked DimSource BRENNAN | 2026-10-20: DataStatus MISSING -&gt; ASSUMED (Brennan catalog only; 1504 / 6807 SPEC exists since batch 17) | leg 1: adjustable ORB tip-to-body-face 1.14 = Air-Way 6801 ORB_I3 for -16 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION); leg 1: adjustable ORB thread length 0.469 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_THDL at every dash -02..-32) for -16 (end library, Q-TRANSFER-ENDLIB 2026-10-08); leg 1: adjustable ORB undercut dia 1.195 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_GRVDIA at every dash -02..-32) for -16 (end library, Q-TRANSFER-ENDLIB 2026-10-08); leg 2: adjustable ORB tip-to-body-face 1.14 = Air-Way 6801 ORB_I3 for -16 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION); leg 2: adjustable ORB thread length 0.469 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_THDL at every dash -02..-32) for -16 (end library, Q-TRANSFER-ENDLIB 2026-10-08); leg 2: adjustable ORB undercut dia 1.195 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_GRVDIA at every dash -02..-32) for -16 (end library, Q-TRANSFER-ENDLIB 2026-10-08)</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>6807-16-16-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6807-20-20-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9425</v>
+      </c>
+      <c r="H4" t="n">
+        <v>75</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.09253</v>
+      </c>
+      <c r="J4" t="n">
+        <v>75</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.9425</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.0825</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.7534999999999999</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.9425</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.09253</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.9425</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.0825</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.7534999999999999</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.93769</v>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>6807-20-20-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>90 deg Adjustable Male ORB x Adjustable Male ORB Elbow, 1 5/8-12 (adjustable male ORB) x 1 5/8-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>6807</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): legs / locknut hexes / flats / bores from the Brennan TFA catalog p.44; ORB majors from the end library | 2026-10-20 (batch 19 D_geom): DataStatus MISSING -&gt; ASSUMED - one source (Brennan TFA catalog p.44 TFA-p044-t01); generated with the batch-17 6807 SPEC | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = the row body hex Y (no male JIC leg, so no 2603HX raise), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing; end-library values (Q-TRANSFER-ENDLIB, user 2026-10-08 'reuse end details - yes'): adjustable ORB tip-to-body-face = Air-Way 6801 ORB_I3 of the same ORB size (= the Brennan 6801 STEPs); adjustable ORB thread length = the ORB end library (6401 / 6405 / 6410 tables, = Air-Way 6801 at every dash); adjustable ORB O-ring undercut dia = the ORB end library (6401 / 6405 / 6410 tables, = Air-Way 6801 at every dash); two adjustable ORB legs on one 90 deg elbow forging (OMi "MAORB - MAORB 90 deg Elbow Forged"; no Brennan 6807 STEP seen: the body form - 2500HX hex arms + 30deg corner puck, each ORB leg = the ORB leg of the accepted 6801 forging - is ASSUMED from the Brennan 6801-XX-XX-NWO-FG STEPs, shape only)</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.44 alone; marked DimSource BRENNAN | 2026-10-20: DataStatus MISSING -&gt; ASSUMED (Brennan catalog only; 1504 / 6807 SPEC exists since batch 17) | leg 1: adjustable ORB tip-to-body-face 1.14 = Air-Way 6801 ORB_I3 for -20 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION); leg 1: adjustable ORB thread length 0.469 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_THDL at every dash -02..-32) for -20 (end library, Q-TRANSFER-ENDLIB 2026-10-08); leg 1: adjustable ORB undercut dia 1.507 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_GRVDIA at every dash -02..-32) for -20 (end library, Q-TRANSFER-ENDLIB 2026-10-08); leg 2: adjustable ORB tip-to-body-face 1.14 = Air-Way 6801 ORB_I3 for -20 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION); leg 2: adjustable ORB thread length 0.469 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_THDL at every dash -02..-32) for -20 (end library, Q-TRANSFER-ENDLIB 2026-10-08); leg 2: adjustable ORB undercut dia 1.507 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_GRVDIA at every dash -02..-32) for -20 (end library, Q-TRANSFER-ENDLIB 2026-10-08)</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>6807-20-20-NWO-FG</t>
         </is>
       </c>
     </row>
